--- a/artfynd/A 52815-2021 artfynd.xlsx
+++ b/artfynd/A 52815-2021 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 52815-2021 artfynd.xlsx
+++ b/artfynd/A 52815-2021 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY10"/>
+  <dimension ref="A1:AY11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,37 +675,32 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>96392635</v>
+        <v>96392561</v>
       </c>
       <c r="B2" t="n">
-        <v>86196</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93207</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>4405</v>
+        <v>789</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Diskvaxskivling</t>
+          <t>Raggtaggsvamp</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Hygrophorus discoideus</t>
+          <t>Hydnellum mirabile</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Pers.) Fr.</t>
+          <t>(Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -718,10 +713,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>711426.0609338259</v>
+        <v>711452</v>
       </c>
       <c r="R2" t="n">
-        <v>6648493.649619375</v>
+        <v>6648476</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -751,19 +746,9 @@
           <t>2021-09-29</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2021-09-29</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -795,37 +780,32 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>96392561</v>
+        <v>96392583</v>
       </c>
       <c r="B3" t="n">
-        <v>90663</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>90639</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>789</v>
+        <v>970</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Raggtaggsvamp</t>
+          <t>Bittermusseron</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Hydnellum mirabile</t>
+          <t>Leucopaxillus gentianeus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Fr.) P.Karst.</t>
+          <t>(Quél.) Kotl.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -838,10 +818,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>711452.2365335284</v>
+        <v>711434</v>
       </c>
       <c r="R3" t="n">
-        <v>6648476.051391803</v>
+        <v>6648466</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -871,19 +851,9 @@
           <t>2021-09-29</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2021-09-29</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -918,12 +888,7 @@
         <v>96392598</v>
       </c>
       <c r="B4" t="n">
-        <v>87982</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>90662</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -958,10 +923,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>711426.0609338259</v>
+        <v>711426</v>
       </c>
       <c r="R4" t="n">
-        <v>6648493.649619375</v>
+        <v>6648493</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -991,19 +956,9 @@
           <t>2021-09-29</t>
         </is>
       </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA4" t="inlineStr">
         <is>
           <t>2021-09-29</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1035,41 +990,44 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>96392599</v>
+        <v>96392566</v>
       </c>
       <c r="B5" t="n">
-        <v>90126</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93205</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>232138</v>
+        <v>2058</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Gul lammticka</t>
+          <t>Koppartaggsvamp</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Albatrellus citrinus</t>
+          <t>Hydnellum lundellii</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Ryman</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr"/>
-      <c r="J5" t="inlineStr"/>
+          <t>(Maas Geest. &amp; Nannf.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K5" t="inlineStr"/>
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
@@ -1078,10 +1036,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>711426.0609338259</v>
+        <v>711452</v>
       </c>
       <c r="R5" t="n">
-        <v>6648493.649619375</v>
+        <v>6648476</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1111,19 +1069,9 @@
           <t>2021-09-29</t>
         </is>
       </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA5" t="inlineStr">
         <is>
           <t>2021-09-29</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1158,12 +1106,7 @@
         <v>96392588</v>
       </c>
       <c r="B6" t="n">
-        <v>88886</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91361</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1198,10 +1141,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>711434.2169134025</v>
+        <v>711434</v>
       </c>
       <c r="R6" t="n">
-        <v>6648465.472391769</v>
+        <v>6648466</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1231,19 +1174,9 @@
           <t>2021-09-29</t>
         </is>
       </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA6" t="inlineStr">
         <is>
           <t>2021-09-29</t>
-        </is>
-      </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1275,15 +1208,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>96392591</v>
+        <v>96392635</v>
       </c>
       <c r="B7" t="n">
-        <v>90674</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>89143</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1291,21 +1219,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>5964</v>
+        <v>4405</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Diskvaxskivling</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus s.str.</t>
+          <t>Hygrophorus discoideus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.:Fr.) P.Karst.</t>
+          <t>(Pers.) Fr.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1318,10 +1246,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>711434.2169134025</v>
+        <v>711426</v>
       </c>
       <c r="R7" t="n">
-        <v>6648465.472391769</v>
+        <v>6648493</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1351,19 +1279,9 @@
           <t>2021-09-29</t>
         </is>
       </c>
-      <c r="Z7" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA7" t="inlineStr">
         <is>
           <t>2021-09-29</t>
-        </is>
-      </c>
-      <c r="AB7" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1395,49 +1313,36 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>96392566</v>
+        <v>96392591</v>
       </c>
       <c r="B8" t="n">
-        <v>90661</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93233</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>2058</v>
+        <v>5964</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Koppartaggsvamp</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Hydnellum lundellii</t>
+          <t>Sarcodon imbricatus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Maas Geest. &amp; Nannf.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="J8" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>(L.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
+      <c r="J8" t="inlineStr"/>
       <c r="K8" t="inlineStr"/>
       <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
@@ -1446,10 +1351,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>711452.2365335284</v>
+        <v>711434</v>
       </c>
       <c r="R8" t="n">
-        <v>6648476.051391803</v>
+        <v>6648466</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1479,19 +1384,9 @@
           <t>2021-09-29</t>
         </is>
       </c>
-      <c r="Z8" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA8" t="inlineStr">
         <is>
           <t>2021-09-29</t>
-        </is>
-      </c>
-      <c r="AB8" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1523,37 +1418,32 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>96392583</v>
+        <v>96392599</v>
       </c>
       <c r="B9" t="n">
-        <v>87960</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92688</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>970</v>
+        <v>232138</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Bittermusseron</t>
+          <t>Gul lammticka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Leucopaxillus gentianeus</t>
+          <t>Albatrellus citrinus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Quél.) Kotl.</t>
+          <t>Ryman</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1566,10 +1456,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>711434.2169134025</v>
+        <v>711426</v>
       </c>
       <c r="R9" t="n">
-        <v>6648465.472391769</v>
+        <v>6648493</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1599,19 +1489,9 @@
           <t>2021-09-29</t>
         </is>
       </c>
-      <c r="Z9" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA9" t="inlineStr">
         <is>
           <t>2021-09-29</t>
-        </is>
-      </c>
-      <c r="AB9" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1643,15 +1523,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>96456055</v>
+        <v>96392615</v>
       </c>
       <c r="B10" t="n">
-        <v>90656</v>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92688</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1659,33 +1534,25 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6003297</v>
+        <v>232138</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Spricktaggsvamp</t>
+          <t>Gul lammticka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Hydnellum glaucopus</t>
+          <t>Albatrellus citrinus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Maas Geest. &amp; Nannf.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J10" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>Ryman</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
+      <c r="J10" t="inlineStr"/>
       <c r="K10" t="inlineStr"/>
       <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
@@ -1694,10 +1561,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>711480.3475536401</v>
+        <v>711414</v>
       </c>
       <c r="R10" t="n">
-        <v>6648451.026067924</v>
+        <v>6648558</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1727,19 +1594,9 @@
           <t>2021-09-29</t>
         </is>
       </c>
-      <c r="Z10" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA10" t="inlineStr">
         <is>
           <t>2021-09-29</t>
-        </is>
-      </c>
-      <c r="AB10" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1760,10 +1617,123 @@
       </c>
       <c r="AX10" t="inlineStr">
         <is>
+          <t>Ossian Rydebjörk, Birgitta Wasstorp, Kristoffer Stighäll</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr">
+        <is>
+          <t>Svampar i Roslagen</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>96456055</v>
+      </c>
+      <c r="B11" t="n">
+        <v>93200</v>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>EN</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>6003297</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Spricktaggsvamp</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Hydnellum glaucopus</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>(Maas Geest. &amp; Nannf.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr"/>
+      <c r="N11" t="inlineStr"/>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>Lomsjön S, Upl</t>
+        </is>
+      </c>
+      <c r="Q11" t="n">
+        <v>711480</v>
+      </c>
+      <c r="R11" t="n">
+        <v>6648451</v>
+      </c>
+      <c r="S11" t="n">
+        <v>10</v>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>Norrtälje</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>Söderby-Karl</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>2021-09-29</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>2021-09-29</t>
+        </is>
+      </c>
+      <c r="AD11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF11" t="inlineStr"/>
+      <c r="AG11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT11" t="inlineStr"/>
+      <c r="AW11" t="inlineStr">
+        <is>
           <t>Ossian Rydebjörk</t>
         </is>
       </c>
-      <c r="AY10" t="inlineStr">
+      <c r="AX11" t="inlineStr">
+        <is>
+          <t>Ossian Rydebjörk</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr">
         <is>
           <t>Svampar i Roslagen</t>
         </is>

--- a/artfynd/A 52815-2021 artfynd.xlsx
+++ b/artfynd/A 52815-2021 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY11"/>
+  <dimension ref="A1:AZ11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -670,6 +670,11 @@
       <c r="AY1" t="inlineStr">
         <is>
           <t>Projektnamn</t>
+        </is>
+      </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
         </is>
       </c>
     </row>
@@ -777,6 +782,11 @@
           <t>Svampar i Roslagen</t>
         </is>
       </c>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96392561</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -882,6 +892,11 @@
           <t>Svampar i Roslagen</t>
         </is>
       </c>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96392583</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -987,6 +1002,11 @@
           <t>Svampar i Roslagen</t>
         </is>
       </c>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96392598</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1098,6 +1118,11 @@
       <c r="AY5" t="inlineStr">
         <is>
           <t>Svampar i Roslagen</t>
+        </is>
+      </c>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96392566</t>
         </is>
       </c>
     </row>
@@ -1205,6 +1230,11 @@
           <t>Svampar i Roslagen</t>
         </is>
       </c>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96392588</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1310,6 +1340,11 @@
           <t>Svampar i Roslagen</t>
         </is>
       </c>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96392635</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1415,6 +1450,11 @@
           <t>Svampar i Roslagen</t>
         </is>
       </c>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96392591</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1520,6 +1560,11 @@
           <t>Svampar i Roslagen</t>
         </is>
       </c>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96392599</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1625,6 +1670,11 @@
           <t>Svampar i Roslagen</t>
         </is>
       </c>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96392615</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1738,8 +1788,25 @@
           <t>Svampar i Roslagen</t>
         </is>
       </c>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96456055</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>